--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484320_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484320_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R. DALET CASALPRIM</t>
+          <t>G. FERRARI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.0248</v>
+        <v>2.2968</v>
       </c>
       <c r="E2" t="n">
-        <v>1.0422</v>
+        <v>1.1261</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9826</v>
+        <v>1.1707</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.7062</v>
+        <v>1.6144</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.1527</v>
+        <v>1.034</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5535</v>
+        <v>0.5803</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0433</v>
+        <v>0.95</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.0781</v>
+        <v>1.0438</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1214</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.7496</v>
+        <v>0.6644</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0747</v>
+        <v>-0.0097</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.6749000000000001</v>
+        <v>0.6741</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3907</v>
+        <v>0.9767</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3907</v>
+        <v>0.9767</v>
       </c>
       <c r="S2" t="n">
-        <v>1.012</v>
+        <v>0.315</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9988</v>
+        <v>0.1761</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0131</v>
+        <v>0.1389</v>
       </c>
       <c r="V2" t="n">
-        <v>1.3283</v>
+        <v>-0.6093</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1.3283</v>
+        <v>-0.6093</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>G. FERRARI</t>
+          <t>R. DALET CASALPRIM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6472</v>
+        <v>1.4998</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7217</v>
+        <v>0.4355</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9256</v>
+        <v>1.0643</v>
       </c>
       <c r="G3" t="n">
-        <v>1.6144</v>
+        <v>-0.7062</v>
       </c>
       <c r="H3" t="n">
-        <v>1.034</v>
+        <v>-0.1527</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5803</v>
+        <v>-0.5535</v>
       </c>
       <c r="J3" t="n">
-        <v>0.95</v>
+        <v>0.0433</v>
       </c>
       <c r="K3" t="n">
-        <v>1.0438</v>
+        <v>-0.0781</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.09379999999999999</v>
+        <v>0.1214</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6644</v>
+        <v>-0.7496</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0097</v>
+        <v>-0.0747</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6741</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9767</v>
+        <v>0.3907</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9767</v>
+        <v>0.3907</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3345</v>
+        <v>0.487</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2283</v>
+        <v>0.3921</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1062</v>
+        <v>0.0949</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.6093</v>
+        <v>1.3283</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.6093</v>
+        <v>1.3283</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. BERTOMEU BALDÉ</t>
+          <t>E. MARTÍN GASCÓN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1068</v>
+        <v>0.0238</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2219</v>
+        <v>-0.7726</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3287</v>
+        <v>0.7964</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.6478</v>
+        <v>-1.757</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.998</v>
+        <v>-3.2538</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3502</v>
+        <v>1.4968</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.1634</v>
+        <v>-0.7088</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.2443</v>
+        <v>-1.9366</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0809</v>
+        <v>1.2278</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4844</v>
+        <v>-1.0482</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7536</v>
+        <v>-1.3172</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2692</v>
+        <v>0.269</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1953</v>
+        <v>1.1721</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1953</v>
+        <v>1.1721</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3456</v>
+        <v>0.6088</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3853</v>
+        <v>-0.0638</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0397</v>
+        <v>0.6725</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. MARTÍN GASCÓN</t>
+          <t>J. BERTOMEU BALDÉ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3456</v>
+        <v>-0.2468</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.2782</v>
+        <v>-0.0815</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9326</v>
+        <v>-0.1653</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.757</v>
+        <v>-0.6478</v>
       </c>
       <c r="H5" t="n">
-        <v>-3.2538</v>
+        <v>-0.998</v>
       </c>
       <c r="I5" t="n">
-        <v>1.4968</v>
+        <v>0.3502</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.7088</v>
+        <v>-0.1634</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.9366</v>
+        <v>-0.2443</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2278</v>
+        <v>0.0809</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.0482</v>
+        <v>-0.4844</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.3172</v>
+        <v>-0.7536</v>
       </c>
       <c r="O5" t="n">
-        <v>0.269</v>
+        <v>0.2692</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1721</v>
+        <v>0.1953</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1721</v>
+        <v>0.1953</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2394</v>
+        <v>0.2057</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5693</v>
+        <v>0.0819</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8087</v>
+        <v>0.1238</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V. MANDIM SILVA</t>
+          <t>J. LLORENTE GUILLEMI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.9003</v>
+        <v>-0.3211</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.173</v>
+        <v>-1.5282</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2728</v>
+        <v>1.2071</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.6377</v>
+        <v>0.7731</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2796</v>
+        <v>1.1376</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9173</v>
+        <v>-0.3646</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4803</v>
+        <v>1.3925</v>
       </c>
       <c r="K6" t="n">
-        <v>1.6666</v>
+        <v>1.352</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.1863</v>
+        <v>0.0405</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.118</v>
+        <v>-0.6194</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.387</v>
+        <v>-0.2144</v>
       </c>
       <c r="O6" t="n">
-        <v>0.269</v>
+        <v>-0.4051</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.3907</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5627</v>
+        <v>0.9767</v>
       </c>
       <c r="S6" t="n">
-        <v>1.0147</v>
+        <v>0.2146</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3001</v>
+        <v>0.029</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7146</v>
+        <v>0.1856</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.8865</v>
+        <v>-0.3321</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.9962</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.8865</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. LLORENTE GUILLEMI</t>
+          <t>E. TURNQUEST</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.064</v>
+        <v>-1.2264</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.1349</v>
+        <v>0.0411</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0709</v>
+        <v>-1.2675</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7731</v>
+        <v>0.0156</v>
       </c>
       <c r="H7" t="n">
-        <v>1.1376</v>
+        <v>-0.1192</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3646</v>
+        <v>0.1348</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3925</v>
+        <v>0.0205</v>
       </c>
       <c r="K7" t="n">
-        <v>1.352</v>
+        <v>0.0205</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0405</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6194</v>
+        <v>-0.0049</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2144</v>
+        <v>-0.1397</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4051</v>
+        <v>0.1348</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5282</v>
+        <v>-0.0234</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5777</v>
+        <v>0.0207</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0495</v>
+        <v>-0.044</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3321</v>
+        <v>-1.2186</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.9962</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6642</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. TURNQUEST</t>
+          <t>V. MANDIM SILVA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4831</v>
+        <v>-1.2271</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1611</v>
+        <v>-1.173</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.322</v>
+        <v>-0.054</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0156</v>
+        <v>-0.6377</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1192</v>
+        <v>0.2796</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1348</v>
+        <v>-0.9173</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0205</v>
+        <v>0.4803</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0205</v>
+        <v>1.6666</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-1.1863</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0049</v>
+        <v>-1.118</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1397</v>
+        <v>-1.387</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1348</v>
+        <v>0.269</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.5627</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2801</v>
+        <v>0.6879</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1816</v>
+        <v>0.3001</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0985</v>
+        <v>0.3878</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2186</v>
+        <v>-0.8865</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2186</v>
+        <v>-0.8865</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0183</v>
+        <v>-1.6567</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.753</v>
+        <v>-2.1463</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7347</v>
+        <v>0.4896</v>
       </c>
       <c r="G9" t="n">
         <v>-2.0089</v>
@@ -1156,13 +1156,13 @@
         <v>0.7814</v>
       </c>
       <c r="S9" t="n">
-        <v>0.186</v>
+        <v>0.5475</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4566</v>
+        <v>0.1501</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6425999999999999</v>
+        <v>0.3975</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. PALOMARES MUÑOZ</t>
+          <t>R. FERNANDEZ DIAZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0388</v>
+        <v>-2.3619</v>
       </c>
       <c r="E10" t="n">
-        <v>1.3545</v>
+        <v>-2.6505</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.3932</v>
+        <v>0.2885</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.7638</v>
+        <v>-2.3989</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.0044</v>
+        <v>-1.8202</v>
       </c>
       <c r="I10" t="n">
-        <v>1.2406</v>
+        <v>-0.5788</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6698</v>
+        <v>-1.165</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.2459</v>
+        <v>-1.5311</v>
       </c>
       <c r="L10" t="n">
-        <v>1.9157</v>
+        <v>0.3662</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.4336</v>
+        <v>-1.234</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7585</v>
+        <v>-0.2891</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6751</v>
+        <v>-0.9449</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1953</v>
+        <v>-0.586</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7814</v>
+        <v>1.3674</v>
       </c>
       <c r="S10" t="n">
-        <v>1.3576</v>
+        <v>0.5682</v>
       </c>
       <c r="T10" t="n">
-        <v>1.3841</v>
+        <v>0.4679</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0265</v>
+        <v>0.1003</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.4373</v>
+        <v>0.0549</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.7145</v>
+        <v>0.0549</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. FERNANDEZ DIAZ</t>
+          <t>R. PALOMARES MUÑOZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.2258</v>
+        <v>-2.976</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.6505</v>
+        <v>0.4444</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4247</v>
+        <v>-3.4205</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.3989</v>
+        <v>-0.7638</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.8202</v>
+        <v>-2.0044</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5788</v>
+        <v>1.2406</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.165</v>
+        <v>0.6698</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.5311</v>
+        <v>-1.2459</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3662</v>
+        <v>1.9157</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.234</v>
+        <v>-1.4336</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2891</v>
+        <v>-0.7585</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9449</v>
+        <v>-0.6751</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.586</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3674</v>
+        <v>0.7814</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7044</v>
+        <v>0.4203</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4679</v>
+        <v>0.4741</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2365</v>
+        <v>-0.0537</v>
       </c>
       <c r="V11" t="n">
-        <v>0.0549</v>
+        <v>-2.4373</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X11" t="n">
-        <v>0.0549</v>
+        <v>-2.7145</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.9895</v>
+        <v>-5.2189</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.9107</v>
+        <v>-3.1129</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.0787</v>
+        <v>-2.106</v>
       </c>
       <c r="G12" t="n">
         <v>-2.5789</v>
@@ -1390,13 +1390,13 @@
         <v>0.586</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5624</v>
+        <v>0.333</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2863</v>
+        <v>0.08409999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2761</v>
+        <v>0.2489</v>
       </c>
       <c r="V12" t="n">
         <v>-1.6056</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.523</v>
+        <v>-5.6085</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.5978</v>
+        <v>-3.9011</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.9252</v>
+        <v>-1.7073</v>
       </c>
       <c r="G13" t="n">
         <v>-4.0861</v>
@@ -1468,13 +1468,13 @@
         <v>0.9767</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2746</v>
+        <v>0.1892</v>
       </c>
       <c r="T13" t="n">
-        <v>0.71</v>
+        <v>0.4067</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4353</v>
+        <v>-0.2175</v>
       </c>
       <c r="V13" t="n">
         <v>1.2186</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-17.0232</v>
+        <v>-17.023</v>
       </c>
       <c r="E14" t="n">
-        <v>-13.3189</v>
+        <v>-13.319</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.703900000000001</v>
+        <v>-3.704</v>
       </c>
       <c r="G14" t="n">
         <v>-13.1822</v>
@@ -1546,13 +1546,13 @@
         <v>9.767099999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>4.553900000000001</v>
+        <v>4.5538</v>
       </c>
       <c r="T14" t="n">
         <v>2.519</v>
       </c>
       <c r="U14" t="n">
-        <v>2.034899999999999</v>
+        <v>2.035</v>
       </c>
       <c r="V14" t="n">
         <v>-4.4876</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.852</v>
+        <v>7.9176</v>
       </c>
       <c r="E15" t="n">
-        <v>4.6633</v>
+        <v>5.27</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1887</v>
+        <v>2.6476</v>
       </c>
       <c r="G15" t="n">
         <v>5.6659</v>
@@ -1624,13 +1624,13 @@
         <v>0.9767</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0093</v>
+        <v>0.0563</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9078000000000001</v>
+        <v>-0.3012</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1014</v>
+        <v>0.3575</v>
       </c>
       <c r="V15" t="n">
         <v>1.2186</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.8561</v>
+        <v>5.4941</v>
       </c>
       <c r="E16" t="n">
-        <v>3.2364</v>
+        <v>3.0342</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6197</v>
+        <v>2.4599</v>
       </c>
       <c r="G16" t="n">
         <v>3.7801</v>
@@ -1702,13 +1702,13 @@
         <v>1.9534</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.4868</v>
+        <v>-0.8488</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1594</v>
+        <v>-0.3617</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.3273</v>
+        <v>-0.4871</v>
       </c>
       <c r="V16" t="n">
         <v>0.6093</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.7354</v>
+        <v>3.3038</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3742</v>
+        <v>0.4642</v>
       </c>
       <c r="F17" t="n">
-        <v>3.3612</v>
+        <v>2.8397</v>
       </c>
       <c r="G17" t="n">
         <v>1.9551</v>
@@ -1780,13 +1780,13 @@
         <v>1.5627</v>
       </c>
       <c r="S17" t="n">
-        <v>2.1943</v>
+        <v>0.7627</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6303</v>
+        <v>-0.2798</v>
       </c>
       <c r="U17" t="n">
-        <v>1.564</v>
+        <v>1.0424</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. YOUNG MEDIERO</t>
+          <t>P. GIMENO MARTIN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.0164</v>
+        <v>1.6169</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7755</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>1.792</v>
+        <v>1.0136</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.9713</v>
+        <v>2.3717</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6042999999999999</v>
+        <v>2.6015</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.5756</v>
+        <v>-0.2298</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.1414</v>
+        <v>2.4115</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4336</v>
+        <v>2.9099</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.575</v>
+        <v>-0.4984</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1701</v>
+        <v>-0.0398</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1707</v>
+        <v>-0.3085</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.2687</v>
       </c>
       <c r="P18" t="n">
-        <v>2.5395</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.9301</v>
       </c>
       <c r="R18" t="n">
-        <v>2.5395</v>
+        <v>1.7581</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1572</v>
+        <v>-0.5241</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4621</v>
+        <v>-0.374</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6952</v>
+        <v>-0.1502</v>
       </c>
       <c r="V18" t="n">
-        <v>1.6056</v>
+        <v>0.9414</v>
       </c>
       <c r="W18" t="n">
-        <v>1.8279</v>
+        <v>1.4959</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2224</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. CAJAL PENACHO</t>
+          <t>A. YOUNG MEDIERO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6328</v>
+        <v>1.5959</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0054</v>
+        <v>-0.5733</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6382</v>
+        <v>2.1692</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0968</v>
+        <v>-1.9713</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3262</v>
+        <v>0.6042999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2294</v>
+        <v>-2.5756</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1019</v>
+        <v>-2.1414</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0614</v>
+        <v>0.4336</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0405</v>
+        <v>-2.575</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0051</v>
+        <v>0.1701</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2648</v>
+        <v>0.1707</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2698</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7814</v>
+        <v>2.5395</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7814</v>
+        <v>2.5395</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2454</v>
+        <v>-0.5778</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1073</v>
+        <v>-0.2598</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1382</v>
+        <v>-0.318</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.6056</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.8279</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.2224</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. GIMENO MARTIN</t>
+          <t>R. DÍAZ DEL VALLE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4253</v>
+        <v>0.8238</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1988</v>
+        <v>-2.7631</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2265</v>
+        <v>3.5869</v>
       </c>
       <c r="G20" t="n">
-        <v>2.3717</v>
+        <v>2.0195</v>
       </c>
       <c r="H20" t="n">
-        <v>2.6015</v>
+        <v>1.5746</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2298</v>
+        <v>0.4449</v>
       </c>
       <c r="J20" t="n">
-        <v>2.4115</v>
+        <v>1.1107</v>
       </c>
       <c r="K20" t="n">
-        <v>2.9099</v>
+        <v>1.0693</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.4984</v>
+        <v>0.0415</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0398</v>
+        <v>0.9088000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3085</v>
+        <v>0.5053</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2687</v>
+        <v>0.4035</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.1721</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q20" t="n">
         <v>-2.9301</v>
       </c>
       <c r="R20" t="n">
-        <v>1.7581</v>
+        <v>2.5395</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.7157</v>
+        <v>-0.3632</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7784</v>
+        <v>-0.5019</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.9373</v>
+        <v>0.1387</v>
       </c>
       <c r="V20" t="n">
-        <v>0.9414</v>
+        <v>-0.4418</v>
       </c>
       <c r="W20" t="n">
-        <v>1.4959</v>
+        <v>-0.4418</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. DÍAZ DEL VALLE</t>
+          <t>D. CAJAL PENACHO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2185</v>
+        <v>0.6794</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.9653</v>
+        <v>0.09569999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>3.1838</v>
+        <v>0.5837</v>
       </c>
       <c r="G21" t="n">
-        <v>2.0195</v>
+        <v>0.0968</v>
       </c>
       <c r="H21" t="n">
-        <v>1.5746</v>
+        <v>0.3262</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4449</v>
+        <v>-0.2294</v>
       </c>
       <c r="J21" t="n">
-        <v>1.1107</v>
+        <v>0.1019</v>
       </c>
       <c r="K21" t="n">
-        <v>1.0693</v>
+        <v>0.0614</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0415</v>
+        <v>0.0405</v>
       </c>
       <c r="M21" t="n">
-        <v>0.9088000000000001</v>
+        <v>-0.0051</v>
       </c>
       <c r="N21" t="n">
-        <v>0.5053</v>
+        <v>0.2648</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4035</v>
+        <v>-0.2698</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.3907</v>
+        <v>0.7814</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.5395</v>
+        <v>0.7814</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9686</v>
+        <v>-0.1988</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7040999999999999</v>
+        <v>-0.0062</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2644</v>
+        <v>-0.1926</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.4418</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.4418</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4738</v>
+        <v>-0.3182</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1611</v>
+        <v>-0.06</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3127</v>
+        <v>-0.2582</v>
       </c>
       <c r="G22" t="n">
         <v>-0.389</v>
@@ -2170,13 +2170,13 @@
         <v>0.1953</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2801</v>
+        <v>-0.1245</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1816</v>
+        <v>-0.0805</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0985</v>
+        <v>-0.044</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.2397</v>
+        <v>-1.3939</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.8613</v>
+        <v>-2.3669</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6216</v>
+        <v>0.973</v>
       </c>
       <c r="G23" t="n">
         <v>-0.3464</v>
@@ -2248,13 +2248,13 @@
         <v>1.3674</v>
       </c>
       <c r="S23" t="n">
-        <v>0.115</v>
+        <v>-0.0392</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6357</v>
+        <v>0.1301</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5207000000000001</v>
+        <v>-0.1694</v>
       </c>
       <c r="V23" t="n">
         <v>0.5545</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>17.023</v>
+        <v>19.7194</v>
       </c>
       <c r="E24" t="n">
         <v>3.7041</v>
       </c>
       <c r="F24" t="n">
-        <v>13.319</v>
+        <v>16.0154</v>
       </c>
       <c r="G24" t="n">
         <v>13.1824</v>
@@ -2299,10 +2299,10 @@
         <v>2.023199999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>9.687000000000001</v>
+        <v>9.686999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>8.331999999999999</v>
+        <v>8.332000000000001</v>
       </c>
       <c r="L24" t="n">
         <v>1.3552</v>
@@ -2326,13 +2326,13 @@
         <v>13.674</v>
       </c>
       <c r="S24" t="n">
-        <v>-4.5538</v>
+        <v>-1.8574</v>
       </c>
       <c r="T24" t="n">
-        <v>-2.0347</v>
+        <v>-2.035</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.519</v>
+        <v>0.1773</v>
       </c>
       <c r="V24" t="n">
         <v>4.4876</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484320_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484320_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -558,7 +563,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -626,6 +631,11 @@
       </c>
       <c r="X2" t="n">
         <v>-0.6093</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484320_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -636,7 +646,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -704,75 +714,80 @@
       </c>
       <c r="X3" t="n">
         <v>1.3283</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484320_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. MARTÍN GASCÓN</t>
+          <t>J. BERTOMEU BALDÉ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0238</v>
+        <v>0.307</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.7726</v>
+        <v>0.307</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7964</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.757</v>
+        <v>0.307</v>
       </c>
       <c r="H4" t="n">
-        <v>-3.2538</v>
+        <v>0.307</v>
       </c>
       <c r="I4" t="n">
-        <v>1.4968</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.7088</v>
+        <v>0.307</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.9366</v>
+        <v>0.307</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2278</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.0482</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.3172</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.269</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6088</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0638</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6725</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -782,75 +797,80 @@
       </c>
       <c r="X4" t="n">
         <v>0</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484320_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. BERTOMEU BALDÉ</t>
+          <t>E. MARTÍN GASCÓN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2468</v>
+        <v>0.307</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0815</v>
+        <v>0.307</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1653</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.6478</v>
+        <v>0.307</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.998</v>
+        <v>0.307</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3502</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.1634</v>
+        <v>0.307</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.2443</v>
+        <v>0.307</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0809</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4844</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7536</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2692</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2057</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0819</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1238</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -860,447 +880,477 @@
       </c>
       <c r="X5" t="n">
         <v>0</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484320_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. LLORENTE GUILLEMI</t>
+          <t>E. MARTIN GASCON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3211</v>
+        <v>-0.2831</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.5282</v>
+        <v>-1.0796</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2071</v>
+        <v>0.7964</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7731</v>
+        <v>-2.064</v>
       </c>
       <c r="H6" t="n">
-        <v>1.1376</v>
+        <v>-3.5608</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3646</v>
+        <v>1.4968</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3925</v>
+        <v>-1.0158</v>
       </c>
       <c r="K6" t="n">
-        <v>1.352</v>
+        <v>-2.2436</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0405</v>
+        <v>1.2278</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6194</v>
+        <v>-1.0482</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2144</v>
+        <v>-1.3172</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4051</v>
+        <v>0.269</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.9767</v>
+        <v>1.1721</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9767</v>
+        <v>1.1721</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2146</v>
+        <v>0.6088</v>
       </c>
       <c r="T6" t="n">
-        <v>0.029</v>
+        <v>-0.0638</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1856</v>
+        <v>0.6725</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.9962</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6642</v>
+        <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484320_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. TURNQUEST</t>
+          <t>J. LLORENTE GUILLEMI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2264</v>
+        <v>-0.3211</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0411</v>
+        <v>-1.5282</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.2675</v>
+        <v>1.2071</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0156</v>
+        <v>0.7731</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1192</v>
+        <v>1.1376</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1348</v>
+        <v>-0.3646</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0205</v>
+        <v>1.3925</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0205</v>
+        <v>1.352</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.0405</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0049</v>
+        <v>-0.6194</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1397</v>
+        <v>-0.2144</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1348</v>
+        <v>-0.4051</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.9767</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0234</v>
+        <v>0.2146</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0207</v>
+        <v>0.029</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.044</v>
+        <v>0.1856</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2186</v>
+        <v>-0.3321</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.9962</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2186</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484320_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>V. MANDIM SILVA</t>
+          <t>J. BERTOMEU BALDE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2271</v>
+        <v>-0.5538</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.173</v>
+        <v>-0.3885</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.054</v>
+        <v>-0.1653</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6377</v>
+        <v>-0.9548</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2796</v>
+        <v>-1.305</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9173</v>
+        <v>0.3502</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4803</v>
+        <v>-0.4704</v>
       </c>
       <c r="K8" t="n">
-        <v>1.6666</v>
+        <v>-0.5513</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.1863</v>
+        <v>0.0809</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.118</v>
+        <v>-0.4844</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.387</v>
+        <v>-0.7536</v>
       </c>
       <c r="O8" t="n">
-        <v>0.269</v>
+        <v>0.2692</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3907</v>
+        <v>0.1953</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5627</v>
+        <v>0.1953</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6879</v>
+        <v>0.2057</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3001</v>
+        <v>0.0819</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3878</v>
+        <v>0.1238</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.8865</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.8865</v>
+        <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484320_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. GARCIA LOPEZ</t>
+          <t>E. TURNQUEST</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6567</v>
+        <v>-1.2264</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1463</v>
+        <v>0.0411</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4896</v>
+        <v>-1.2675</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.0089</v>
+        <v>0.0156</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.0336</v>
+        <v>-0.1192</v>
       </c>
       <c r="I9" t="n">
-        <v>1.0247</v>
+        <v>0.1348</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.3196</v>
+        <v>0.0205</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.6145</v>
+        <v>0.0205</v>
       </c>
       <c r="L9" t="n">
-        <v>1.2949</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6893</v>
+        <v>-0.0049</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.419</v>
+        <v>-0.1397</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2702</v>
+        <v>0.1348</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5475</v>
+        <v>-0.0234</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1501</v>
+        <v>0.0207</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3975</v>
+        <v>-0.044</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484320_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. FERNANDEZ DIAZ</t>
+          <t>V. MANDIM SILVA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3619</v>
+        <v>-1.2271</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6505</v>
+        <v>-1.173</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2885</v>
+        <v>-0.054</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.3989</v>
+        <v>-0.6377</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.8202</v>
+        <v>0.2796</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5788</v>
+        <v>-0.9173</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.165</v>
+        <v>0.4803</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.5311</v>
+        <v>1.6666</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3662</v>
+        <v>-1.1863</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.234</v>
+        <v>-1.118</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2891</v>
+        <v>-1.387</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.9449</v>
+        <v>0.269</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.586</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3674</v>
+        <v>1.5627</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5682</v>
+        <v>0.6879</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4679</v>
+        <v>0.3001</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1003</v>
+        <v>0.3878</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0549</v>
+        <v>-0.8865</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0549</v>
+        <v>-0.8865</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484320_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. PALOMARES MUÑOZ</t>
+          <t>M. GARCIA LOPEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.976</v>
+        <v>-1.6567</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4444</v>
+        <v>-2.1463</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.4205</v>
+        <v>0.4896</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.7638</v>
+        <v>-2.0089</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.0044</v>
+        <v>-3.0336</v>
       </c>
       <c r="I11" t="n">
-        <v>1.2406</v>
+        <v>1.0247</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6698</v>
+        <v>-1.3196</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.2459</v>
+        <v>-2.6145</v>
       </c>
       <c r="L11" t="n">
-        <v>1.9157</v>
+        <v>1.2949</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.4336</v>
+        <v>-0.6893</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7585</v>
+        <v>-0.419</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6751</v>
+        <v>-0.2702</v>
       </c>
       <c r="P11" t="n">
         <v>-0.1953</v>
@@ -1312,418 +1362,444 @@
         <v>0.7814</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4203</v>
+        <v>0.5475</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4741</v>
+        <v>0.1501</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0537</v>
+        <v>0.3975</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.4373</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.7145</v>
+        <v>0</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484320_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. FONTANALS MARTIN</t>
+          <t>R. FERNANDEZ DIAZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.2189</v>
+        <v>-2.3619</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.1129</v>
+        <v>-2.6505</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.106</v>
+        <v>0.2885</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.5789</v>
+        <v>-2.3989</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.1763</v>
+        <v>-1.8202</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.4027</v>
+        <v>-0.5788</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.8567</v>
+        <v>-1.165</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4106</v>
+        <v>-1.5311</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.2673</v>
+        <v>0.3662</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.7223</v>
+        <v>-1.234</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.5868</v>
+        <v>-0.2891</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1354</v>
+        <v>-0.9449</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.3674</v>
+        <v>-0.586</v>
       </c>
       <c r="Q12" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R12" t="n">
-        <v>0.586</v>
+        <v>1.3674</v>
       </c>
       <c r="S12" t="n">
-        <v>0.333</v>
+        <v>0.5682</v>
       </c>
       <c r="T12" t="n">
-        <v>0.08409999999999999</v>
+        <v>0.4679</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2489</v>
+        <v>0.1003</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.6056</v>
+        <v>0.0549</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.3869</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2186</v>
+        <v>0.0549</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484320_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. MARTÍNEZ SERRANO</t>
+          <t>R. PALOMARES MUNOZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.6085</v>
+        <v>-2.976</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.9011</v>
+        <v>0.4444</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.7073</v>
+        <v>-3.4205</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.0861</v>
+        <v>-0.7638</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.0522</v>
+        <v>-2.0044</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.0339</v>
+        <v>1.2406</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.8382</v>
+        <v>0.6698</v>
       </c>
       <c r="K13" t="n">
-        <v>0.33</v>
+        <v>-1.2459</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.1682</v>
+        <v>1.9157</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.248</v>
+        <v>-1.4336</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.3822</v>
+        <v>-0.7585</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1342</v>
+        <v>-0.6751</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.9301</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.9069</v>
+        <v>-0.9767</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9767</v>
+        <v>0.7814</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1892</v>
+        <v>0.4203</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4067</v>
+        <v>0.4741</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2175</v>
+        <v>-0.0537</v>
       </c>
       <c r="V13" t="n">
-        <v>1.2186</v>
+        <v>-2.4373</v>
       </c>
       <c r="W13" t="n">
-        <v>2.4373</v>
+        <v>0.2772</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.2186</v>
+        <v>-2.7145</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484320_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>M. FONTANALS MARTIN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-17.023</v>
+        <v>-5.2189</v>
       </c>
       <c r="E14" t="n">
-        <v>-13.319</v>
+        <v>-3.1129</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.704</v>
+        <v>-2.106</v>
       </c>
       <c r="G14" t="n">
-        <v>-13.1822</v>
+        <v>-2.5789</v>
       </c>
       <c r="H14" t="n">
-        <v>-11.1592</v>
+        <v>-1.1763</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.023400000000001</v>
+        <v>-1.4027</v>
       </c>
       <c r="J14" t="n">
-        <v>-3.4953</v>
+        <v>-0.8567</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.827</v>
+        <v>0.4106</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.6682000000000001</v>
+        <v>-1.2673</v>
       </c>
       <c r="M14" t="n">
-        <v>-9.6873</v>
+        <v>-1.7223</v>
       </c>
       <c r="N14" t="n">
-        <v>-8.331900000000001</v>
+        <v>-1.5868</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.3553</v>
+        <v>-0.1354</v>
       </c>
       <c r="P14" t="n">
-        <v>-3.9067</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q14" t="n">
-        <v>-13.6739</v>
+        <v>-1.9534</v>
       </c>
       <c r="R14" t="n">
-        <v>9.767099999999999</v>
+        <v>0.586</v>
       </c>
       <c r="S14" t="n">
-        <v>4.5538</v>
+        <v>0.333</v>
       </c>
       <c r="T14" t="n">
-        <v>2.519</v>
+        <v>0.08409999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>2.035</v>
+        <v>0.2489</v>
       </c>
       <c r="V14" t="n">
-        <v>-4.4876</v>
+        <v>-1.6056</v>
       </c>
       <c r="W14" t="n">
-        <v>1.3314</v>
+        <v>-0.3869</v>
       </c>
       <c r="X14" t="n">
-        <v>-5.8187</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484320_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ MANZANARES</t>
+          <t>P. MARTINEZ SERRANO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>C.B. CUARTE DE HUERVA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.9176</v>
+        <v>-5.6085</v>
       </c>
       <c r="E15" t="n">
-        <v>5.27</v>
+        <v>-3.9011</v>
       </c>
       <c r="F15" t="n">
-        <v>2.6476</v>
+        <v>-1.7073</v>
       </c>
       <c r="G15" t="n">
-        <v>5.6659</v>
+        <v>-4.0861</v>
       </c>
       <c r="H15" t="n">
-        <v>1.8887</v>
+        <v>-1.0522</v>
       </c>
       <c r="I15" t="n">
-        <v>3.7771</v>
+        <v>-3.0339</v>
       </c>
       <c r="J15" t="n">
-        <v>5.0166</v>
+        <v>-2.8382</v>
       </c>
       <c r="K15" t="n">
-        <v>2.0478</v>
+        <v>0.33</v>
       </c>
       <c r="L15" t="n">
-        <v>2.9688</v>
+        <v>-3.1682</v>
       </c>
       <c r="M15" t="n">
-        <v>0.6492</v>
+        <v>-1.248</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1591</v>
+        <v>-1.3822</v>
       </c>
       <c r="O15" t="n">
-        <v>0.8083</v>
+        <v>0.1342</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9767</v>
+        <v>-2.9301</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-3.9069</v>
       </c>
       <c r="R15" t="n">
         <v>0.9767</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0563</v>
+        <v>0.1892</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3012</v>
+        <v>0.4067</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3575</v>
+        <v>-0.2175</v>
       </c>
       <c r="V15" t="n">
         <v>1.2186</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5545</v>
+        <v>2.4373</v>
       </c>
       <c r="X15" t="n">
-        <v>0.6642</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484320_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. MENENDEZ PEREZ</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>C.B. CUARTE DE HUERVA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.4941</v>
+        <v>-17.0229</v>
       </c>
       <c r="E16" t="n">
-        <v>3.0342</v>
+        <v>-13.319</v>
       </c>
       <c r="F16" t="n">
-        <v>2.4599</v>
+        <v>-3.704</v>
       </c>
       <c r="G16" t="n">
-        <v>3.7801</v>
+        <v>-13.1822</v>
       </c>
       <c r="H16" t="n">
-        <v>3.0517</v>
+        <v>-11.1592</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7284</v>
+        <v>-2.023400000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>2.7865</v>
+        <v>-3.4953</v>
       </c>
       <c r="K16" t="n">
-        <v>1.5183</v>
+        <v>-2.827</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2683</v>
+        <v>-0.6682000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9936</v>
+        <v>-9.6873</v>
       </c>
       <c r="N16" t="n">
-        <v>1.5334</v>
+        <v>-8.331900000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5399</v>
+        <v>-1.3553</v>
       </c>
       <c r="P16" t="n">
-        <v>1.9534</v>
+        <v>-3.9067</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-13.6739</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9534</v>
+        <v>9.767099999999999</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8488</v>
+        <v>4.5538</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3617</v>
+        <v>2.519</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4871</v>
+        <v>2.035</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6093</v>
+        <v>-4.4876</v>
       </c>
       <c r="W16" t="n">
-        <v>0.6093</v>
+        <v>1.3314</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
-      </c>
+        <v>-5.8187</v>
+      </c>
+      <c r="Y16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. PORTALEZ MUR</t>
+          <t>J. FERNANDEZ MANZANARES</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.3038</v>
+        <v>7.9176</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4642</v>
+        <v>5.27</v>
       </c>
       <c r="F17" t="n">
-        <v>2.8397</v>
+        <v>2.6476</v>
       </c>
       <c r="G17" t="n">
-        <v>1.9551</v>
+        <v>5.6659</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7005</v>
+        <v>1.8887</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2546</v>
+        <v>3.7771</v>
       </c>
       <c r="J17" t="n">
-        <v>0.502</v>
+        <v>5.0166</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.0793</v>
+        <v>2.0478</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5813</v>
+        <v>2.9688</v>
       </c>
       <c r="M17" t="n">
-        <v>1.4531</v>
+        <v>0.6492</v>
       </c>
       <c r="N17" t="n">
-        <v>0.7798</v>
+        <v>-0.1591</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6733</v>
+        <v>0.8083</v>
       </c>
       <c r="P17" t="n">
-        <v>0.586</v>
+        <v>0.9767</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5627</v>
+        <v>0.9767</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7627</v>
+        <v>0.0563</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2798</v>
+        <v>-0.3012</v>
       </c>
       <c r="U17" t="n">
-        <v>1.0424</v>
+        <v>0.3575</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2186</v>
+        <v>0.5545</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2186</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484320_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. GIMENO MARTIN</t>
+          <t>S. MENENDEZ PEREZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.6169</v>
+        <v>5.4941</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6032999999999999</v>
+        <v>3.0342</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0136</v>
+        <v>2.4599</v>
       </c>
       <c r="G18" t="n">
-        <v>2.3717</v>
+        <v>3.7801</v>
       </c>
       <c r="H18" t="n">
-        <v>2.6015</v>
+        <v>3.0517</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2298</v>
+        <v>0.7284</v>
       </c>
       <c r="J18" t="n">
-        <v>2.4115</v>
+        <v>2.7865</v>
       </c>
       <c r="K18" t="n">
-        <v>2.9099</v>
+        <v>1.5183</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.4984</v>
+        <v>1.2683</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0398</v>
+        <v>0.9936</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3085</v>
+        <v>1.5334</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2687</v>
+        <v>-0.5399</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.1721</v>
+        <v>1.9534</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7581</v>
+        <v>1.9534</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5241</v>
+        <v>-0.8488</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.374</v>
+        <v>-0.3617</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1502</v>
+        <v>-0.4871</v>
       </c>
       <c r="V18" t="n">
-        <v>0.9414</v>
+        <v>0.6093</v>
       </c>
       <c r="W18" t="n">
-        <v>1.4959</v>
+        <v>0.6093</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484320_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. YOUNG MEDIERO</t>
+          <t>M. PORTALEZ MUR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1977,72 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.5959</v>
+        <v>3.3038</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5733</v>
+        <v>0.4642</v>
       </c>
       <c r="F19" t="n">
-        <v>2.1692</v>
+        <v>2.8397</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.9713</v>
+        <v>1.9551</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6042999999999999</v>
+        <v>0.7005</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.5756</v>
+        <v>1.2546</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.1414</v>
+        <v>0.502</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4336</v>
+        <v>-0.0793</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.575</v>
+        <v>0.5813</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1701</v>
+        <v>1.4531</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1707</v>
+        <v>0.7798</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.6733</v>
       </c>
       <c r="P19" t="n">
-        <v>2.5395</v>
+        <v>0.586</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
-        <v>2.5395</v>
+        <v>1.5627</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5778</v>
+        <v>0.7627</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2598</v>
+        <v>-0.2798</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.318</v>
+        <v>1.0424</v>
       </c>
       <c r="V19" t="n">
-        <v>1.6056</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.8279</v>
+        <v>1.2186</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2224</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484320_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8238</v>
+        <v>2.7419</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.7631</v>
+        <v>2.7419</v>
       </c>
       <c r="F20" t="n">
-        <v>3.5869</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>2.0195</v>
+        <v>2.7419</v>
       </c>
       <c r="H20" t="n">
-        <v>1.5746</v>
+        <v>0.921</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4449</v>
+        <v>1.821</v>
       </c>
       <c r="J20" t="n">
-        <v>1.1107</v>
+        <v>2.7419</v>
       </c>
       <c r="K20" t="n">
-        <v>1.0693</v>
+        <v>0.921</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0415</v>
+        <v>1.821</v>
       </c>
       <c r="M20" t="n">
-        <v>0.9088000000000001</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0.5053</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4035</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.5395</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3632</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5019</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1387</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.4418</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.4418</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484320_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. CAJAL PENACHO</t>
+          <t>P. GIMENO MARTIN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6794</v>
+        <v>1.6169</v>
       </c>
       <c r="E21" t="n">
-        <v>0.09569999999999999</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5837</v>
+        <v>1.0136</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0968</v>
+        <v>2.3717</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3262</v>
+        <v>2.6015</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2294</v>
+        <v>-0.2298</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1019</v>
+        <v>2.4115</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0614</v>
+        <v>2.9099</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0405</v>
+        <v>-0.4984</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.0051</v>
+        <v>-0.0398</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2648</v>
+        <v>-0.3085</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2698</v>
+        <v>0.2687</v>
       </c>
       <c r="P21" t="n">
-        <v>0.7814</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.9301</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7814</v>
+        <v>1.7581</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1988</v>
+        <v>-0.5241</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0062</v>
+        <v>-0.374</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1926</v>
+        <v>-0.1502</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.9414</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.4959</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484320_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. PACÍFICO CANTARELLI</t>
+          <t>A. YOUNG MEDIERO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3182</v>
+        <v>1.5959</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.06</v>
+        <v>-0.5733</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2582</v>
+        <v>2.1692</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.389</v>
+        <v>-1.9713</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1192</v>
+        <v>0.6042999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2698</v>
+        <v>-2.5756</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0205</v>
+        <v>-2.1414</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0205</v>
+        <v>0.4336</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>-2.575</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.4095</v>
+        <v>0.1701</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1397</v>
+        <v>0.1707</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2698</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P22" t="n">
-        <v>0.1953</v>
+        <v>2.5395</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.1953</v>
+        <v>2.5395</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1245</v>
+        <v>-0.5778</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0805</v>
+        <v>-0.2598</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.044</v>
+        <v>-0.318</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.6056</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.8279</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.2224</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484320_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>N. CLEDJO HOUNGUES</t>
+          <t>D. CAJAL PENACHO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.3939</v>
+        <v>0.6794</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.3669</v>
+        <v>0.09569999999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>0.973</v>
+        <v>0.5837</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.3464</v>
+        <v>0.0968</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5308</v>
+        <v>0.3262</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.8772</v>
+        <v>-0.2294</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.1213</v>
+        <v>0.1019</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3505</v>
+        <v>0.0614</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.4718</v>
+        <v>0.0405</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.2251</v>
+        <v>-0.0051</v>
       </c>
       <c r="N23" t="n">
-        <v>0.1804</v>
+        <v>0.2648</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4054</v>
+        <v>-0.2698</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.5627</v>
+        <v>0.7814</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3674</v>
+        <v>0.7814</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0392</v>
+        <v>-0.1988</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1301</v>
+        <v>-0.0062</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1694</v>
+        <v>-0.1926</v>
       </c>
       <c r="V23" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484320_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>M. PACIFICO CANTARELLI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,68 +2392,318 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
+        <v>-0.3182</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-0.2582</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-0.389</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-0.1192</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-0.2698</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.0205</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.0205</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-0.4095</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-0.1397</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-0.2698</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-0.1245</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.0805</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-0.044</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484320_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>N. CLEDJO HOUNGUES</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>C.B. CUARTE DE HUERVA</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-1.3939</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-2.3669</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.973</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-0.3464</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.5308</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-0.8772</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-0.1213</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.3505</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-0.4718</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-0.2251</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.1804</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.4054</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-1.5627</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.0392</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.1301</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-0.1694</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0.5545</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0.5545</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484320_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>R. DIAZ DEL VALLE</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>C.B. CUARTE DE HUERVA</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-1.9181</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-5.505</v>
+      </c>
+      <c r="F26" t="n">
+        <v>3.5869</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-0.7224</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.6536</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-1.376</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-1.6312</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.1483</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-1.7795</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.9088000000000001</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.5053</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.4035</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-0.3907</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="R26" t="n">
+        <v>2.5395</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-0.3632</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-0.5019</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.1387</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-0.4418</v>
+      </c>
+      <c r="W26" t="n">
+        <v>-0.4418</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484320_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>C.B. CUARTE DE HUERVA</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
         <v>19.7194</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E27" t="n">
         <v>3.7041</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F27" t="n">
         <v>16.0154</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G27" t="n">
         <v>13.1824</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H27" t="n">
         <v>11.1591</v>
       </c>
-      <c r="I24" t="n">
-        <v>2.023199999999999</v>
-      </c>
-      <c r="J24" t="n">
-        <v>9.686999999999999</v>
-      </c>
-      <c r="K24" t="n">
+      <c r="I27" t="n">
+        <v>2.023299999999999</v>
+      </c>
+      <c r="J27" t="n">
+        <v>9.687000000000001</v>
+      </c>
+      <c r="K27" t="n">
         <v>8.332000000000001</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L27" t="n">
         <v>1.3552</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M27" t="n">
         <v>3.4953</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N27" t="n">
         <v>2.8271</v>
       </c>
-      <c r="O24" t="n">
+      <c r="O27" t="n">
         <v>0.6683000000000001</v>
       </c>
-      <c r="P24" t="n">
+      <c r="P27" t="n">
         <v>3.9068</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q27" t="n">
         <v>-9.766999999999999</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R27" t="n">
         <v>13.674</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S27" t="n">
         <v>-1.8574</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T27" t="n">
         <v>-2.035</v>
       </c>
-      <c r="U24" t="n">
-        <v>0.1773</v>
-      </c>
-      <c r="V24" t="n">
+      <c r="U27" t="n">
+        <v>0.1773000000000001</v>
+      </c>
+      <c r="V27" t="n">
         <v>4.4876</v>
       </c>
-      <c r="W24" t="n">
+      <c r="W27" t="n">
         <v>5.8189</v>
       </c>
-      <c r="X24" t="n">
+      <c r="X27" t="n">
         <v>-1.3313</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
